--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="97">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -82,6 +85,42 @@
     <t>2026-05-14</t>
   </si>
   <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1157 Пловдив Тракия</t>
+  </si>
+  <si>
     <t>В2487ВН</t>
   </si>
   <si>
@@ -109,37 +148,145 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>13:02</t>
-  </si>
-  <si>
-    <t>14:11</t>
-  </si>
-  <si>
-    <t>14:44</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>06:58</t>
-  </si>
-  <si>
-    <t>11:03</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>21:53</t>
-  </si>
-  <si>
-    <t>18:18</t>
-  </si>
-  <si>
-    <t>20:21</t>
-  </si>
-  <si>
-    <t>11:29</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:01:00</t>
+  </si>
+  <si>
+    <t>14:10:00</t>
+  </si>
+  <si>
+    <t>14:43:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>06:57:00</t>
+  </si>
+  <si>
+    <t>11:03:00</t>
+  </si>
+  <si>
+    <t>18:19:00</t>
+  </si>
+  <si>
+    <t>21:52:00</t>
+  </si>
+  <si>
+    <t>18:17:00</t>
+  </si>
+  <si>
+    <t>20:21:00</t>
+  </si>
+  <si>
+    <t>11:29:00</t>
+  </si>
+  <si>
+    <t>13:53:00</t>
+  </si>
+  <si>
+    <t>15:21:00</t>
+  </si>
+  <si>
+    <t>06:54:00</t>
+  </si>
+  <si>
+    <t>16:05:00</t>
+  </si>
+  <si>
+    <t>15:53:00</t>
+  </si>
+  <si>
+    <t>08:55:00</t>
+  </si>
+  <si>
+    <t>21:07:00</t>
+  </si>
+  <si>
+    <t>05:52:00</t>
+  </si>
+  <si>
+    <t>16:03:00</t>
+  </si>
+  <si>
+    <t>06:40:00</t>
+  </si>
+  <si>
+    <t>06:56:00</t>
+  </si>
+  <si>
+    <t>16:09:00</t>
+  </si>
+  <si>
+    <t>3231328834 3231328834</t>
+  </si>
+  <si>
+    <t>3231373058 3231373058</t>
+  </si>
+  <si>
+    <t>3231505560 3231505560</t>
+  </si>
+  <si>
+    <t>3231514660 3231514660</t>
+  </si>
+  <si>
+    <t>3231516387 3231516387</t>
+  </si>
+  <si>
+    <t>3231533652 3231533652</t>
+  </si>
+  <si>
+    <t>3231603156 3231603156</t>
+  </si>
+  <si>
+    <t>3231640580 3231640580</t>
+  </si>
+  <si>
+    <t>3231750126 3231750126</t>
+  </si>
+  <si>
+    <t>3231830298 3231830298</t>
+  </si>
+  <si>
+    <t>3231864854 3231864854</t>
+  </si>
+  <si>
+    <t>3231967281 3231967281</t>
+  </si>
+  <si>
+    <t>3232067639 3232067639</t>
+  </si>
+  <si>
+    <t>3232088987 3232088987</t>
+  </si>
+  <si>
+    <t>3232153642 3232153642</t>
+  </si>
+  <si>
+    <t>3232154850 3232154850</t>
+  </si>
+  <si>
+    <t>3232189049 3232189049</t>
+  </si>
+  <si>
+    <t>3232198270 3232198270</t>
+  </si>
+  <si>
+    <t>3232316334 3232316334</t>
+  </si>
+  <si>
+    <t>3232388224 3232388224</t>
+  </si>
+  <si>
+    <t>3232442599 3232442599</t>
+  </si>
+  <si>
+    <t>3232505328 3232505328</t>
+  </si>
+  <si>
+    <t>3232577414 3232577414</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДИЛЯНА-02 ЕООД</t>
@@ -563,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -572,16 +719,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -621,529 +769,1093 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1147</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F2">
         <v>375.47</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2">
         <v>1.68</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>630.79</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>675.85</v>
       </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="L2" t="s">
+        <v>45</v>
       </c>
       <c r="M2">
-        <v>101702</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1147</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F3">
         <v>436.68</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3">
         <v>1.68</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>733.62</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.8</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>786.02</v>
       </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="L3" t="s">
+        <v>46</v>
       </c>
       <c r="M3">
-        <v>101953</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1147</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F4">
         <v>458.76</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4">
         <v>1.68</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>770.72</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.8</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>825.77</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>33</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>177234</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>1199</v>
-      </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F5">
         <v>56.83</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5">
         <v>1.68</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>95.47</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.8</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>102.29</v>
       </c>
-      <c r="K5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="L5" t="s">
+        <v>48</v>
       </c>
       <c r="M5">
-        <v>264721</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1147</v>
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F6">
         <v>330</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6">
         <v>1.68</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>554.4</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.8</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>594</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>35</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>103101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>1147</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>483.47</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7">
         <v>1.68</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>812.23</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.8</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>870.25</v>
       </c>
-      <c r="K7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="L7" t="s">
+        <v>50</v>
       </c>
       <c r="M7">
-        <v>177572</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>1147</v>
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F8">
         <v>370</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8">
         <v>1.67</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>617.9</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.79</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>662.3</v>
       </c>
-      <c r="K8" t="s">
-        <v>37</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="L8" t="s">
+        <v>51</v>
       </c>
       <c r="M8">
-        <v>103828</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9">
-        <v>1147</v>
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F9">
         <v>469.06</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9">
         <v>1.67</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>783.33</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.79</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>839.62</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
         <v>38</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>178963</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <v>1147</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F10">
         <v>410</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10">
         <v>1.67</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>684.7</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.79</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>733.9</v>
       </c>
-      <c r="K10" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" t="s">
+        <v>53</v>
       </c>
       <c r="M10">
-        <v>104721</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11">
-        <v>1147</v>
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>490</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11">
         <v>1.67</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>818.3</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.78</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>872.2</v>
       </c>
-      <c r="K11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
+      <c r="L11" t="s">
+        <v>54</v>
       </c>
       <c r="M11">
-        <v>180816</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12">
-        <v>1147</v>
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F12">
         <v>494.9</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12">
         <v>1.67</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>826.48</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.77</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>875.97</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13">
+        <v>452.29</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13">
+        <v>1.66</v>
+      </c>
+      <c r="I13" s="1">
+        <v>750.8</v>
+      </c>
+      <c r="J13">
+        <v>1.76</v>
+      </c>
+      <c r="K13" s="1">
+        <v>796.03</v>
+      </c>
+      <c r="L13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>181074</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="3" t="s">
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14">
+        <v>54.55</v>
+      </c>
+      <c r="G14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14">
+        <v>1.66</v>
+      </c>
+      <c r="I14" s="1">
+        <v>90.55</v>
+      </c>
+      <c r="J14">
+        <v>1.75</v>
+      </c>
+      <c r="K14" s="1">
+        <v>95.45999999999999</v>
+      </c>
+      <c r="L14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15">
+        <v>425</v>
+      </c>
+      <c r="G15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15">
+        <v>1.65</v>
+      </c>
+      <c r="I15" s="1">
+        <v>701.25</v>
+      </c>
+      <c r="J15">
+        <v>1.75</v>
+      </c>
+      <c r="K15" s="1">
+        <v>743.75</v>
+      </c>
+      <c r="L15" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16">
+        <v>340</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16">
+        <v>1.65</v>
+      </c>
+      <c r="I16" s="1">
+        <v>561</v>
+      </c>
+      <c r="J16">
+        <v>1.75</v>
+      </c>
+      <c r="K16" s="1">
+        <v>595</v>
+      </c>
+      <c r="L16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17">
+        <v>542.91</v>
+      </c>
+      <c r="G17" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17">
+        <v>1.65</v>
+      </c>
+      <c r="I17" s="1">
+        <v>895.8</v>
+      </c>
+      <c r="J17">
+        <v>1.75</v>
+      </c>
+      <c r="K17" s="1">
+        <v>950.09</v>
+      </c>
+      <c r="L17" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18">
+        <v>57.3</v>
+      </c>
+      <c r="G18" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18">
+        <v>1.65</v>
+      </c>
+      <c r="I18" s="1">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="J18">
+        <v>1.75</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100.28</v>
+      </c>
+      <c r="L18" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19">
+        <v>58.76</v>
+      </c>
+      <c r="G19" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19">
+        <v>1.65</v>
+      </c>
+      <c r="I19" s="1">
+        <v>96.95</v>
+      </c>
+      <c r="J19">
+        <v>1.75</v>
+      </c>
+      <c r="K19" s="1">
+        <v>102.83</v>
+      </c>
+      <c r="L19" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20">
+        <v>373.24</v>
+      </c>
+      <c r="G20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20">
+        <v>1.65</v>
+      </c>
+      <c r="I20" s="1">
+        <v>615.85</v>
+      </c>
+      <c r="J20">
+        <v>1.72</v>
+      </c>
+      <c r="K20" s="1">
+        <v>641.97</v>
+      </c>
+      <c r="L20" t="s">
+        <v>63</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21">
+        <v>48.62</v>
+      </c>
+      <c r="G21" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21">
+        <v>1.65</v>
+      </c>
+      <c r="I21" s="1">
+        <v>80.22</v>
+      </c>
+      <c r="J21">
+        <v>1.75</v>
+      </c>
+      <c r="K21" s="1">
+        <v>85.08</v>
+      </c>
+      <c r="L21" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22">
+        <v>430</v>
+      </c>
+      <c r="G22" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22">
+        <v>1.65</v>
+      </c>
+      <c r="I22" s="1">
+        <v>709.5</v>
+      </c>
+      <c r="J22">
+        <v>1.72</v>
+      </c>
+      <c r="K22" s="1">
+        <v>739.6</v>
+      </c>
+      <c r="L22" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="6">
-        <v>4375.17</v>
-      </c>
-      <c r="C17" s="6">
-        <v>11</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1.6749</v>
-      </c>
-      <c r="E17" s="6">
-        <v>7327.94</v>
-      </c>
-      <c r="F17" s="6">
-        <v>7838.17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="9">
-        <v>4375.17</v>
-      </c>
-      <c r="C18" s="9">
-        <v>11</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="9">
-        <v>7327.94</v>
-      </c>
-      <c r="F18" s="9">
-        <v>7838.17</v>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23">
+        <v>396.8</v>
+      </c>
+      <c r="G23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23">
+        <v>1.65</v>
+      </c>
+      <c r="I23" s="1">
+        <v>654.72</v>
+      </c>
+      <c r="J23">
+        <v>1.71</v>
+      </c>
+      <c r="K23" s="1">
+        <v>678.53</v>
+      </c>
+      <c r="L23" t="s">
+        <v>66</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24">
+        <v>450</v>
+      </c>
+      <c r="G24" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24">
+        <v>1.64</v>
+      </c>
+      <c r="I24" s="1">
+        <v>738</v>
+      </c>
+      <c r="J24">
+        <v>1.7</v>
+      </c>
+      <c r="K24" s="1">
+        <v>765</v>
+      </c>
+      <c r="L24" t="s">
+        <v>67</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="6">
+        <v>8004.64</v>
+      </c>
+      <c r="C29" s="6">
+        <v>23</v>
+      </c>
+      <c r="D29" s="7">
+        <v>1.6637</v>
+      </c>
+      <c r="E29" s="6">
+        <v>13317.12</v>
+      </c>
+      <c r="F29" s="6">
+        <v>14131.79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="9">
+        <v>8004.64</v>
+      </c>
+      <c r="C30" s="9">
+        <v>23</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" s="9">
+        <v>13317.12</v>
+      </c>
+      <c r="F30" s="9">
+        <v>14131.79</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
@@ -340,7 +340,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,12 +350,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,17 +399,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="99">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -94,10 +103,19 @@
     <t>2026-06-24</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>В2487ВН</t>
@@ -127,70 +145,154 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-01 07:17:04</t>
-  </si>
-  <si>
-    <t>2026-06-01 20:44:28</t>
-  </si>
-  <si>
-    <t>2026-06-02 16:50:20</t>
-  </si>
-  <si>
-    <t>2026-06-04 07:15:51</t>
-  </si>
-  <si>
-    <t>2026-06-06 07:06:56</t>
-  </si>
-  <si>
-    <t>2026-06-08 18:19:34</t>
-  </si>
-  <si>
-    <t>2026-06-09 20:12:32</t>
-  </si>
-  <si>
-    <t>2026-06-10 16:25:26</t>
-  </si>
-  <si>
-    <t>2026-06-11 15:14:39</t>
-  </si>
-  <si>
-    <t>2026-06-12 06:52:21</t>
-  </si>
-  <si>
-    <t>2026-06-12 17:36:55</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:11:13</t>
-  </si>
-  <si>
-    <t>2026-06-16 06:38:54</t>
-  </si>
-  <si>
-    <t>2026-06-18 10:47:29</t>
-  </si>
-  <si>
-    <t>2026-06-18 15:42:12</t>
-  </si>
-  <si>
-    <t>2026-06-20 16:57:11</t>
-  </si>
-  <si>
-    <t>2026-06-20 18:40:36</t>
-  </si>
-  <si>
-    <t>2026-06-23 08:05:54</t>
-  </si>
-  <si>
-    <t>2026-06-23 09:34:34</t>
-  </si>
-  <si>
-    <t>2026-06-24 05:40:12</t>
-  </si>
-  <si>
-    <t>2026-06-24 12:52:25</t>
-  </si>
-  <si>
-    <t>2026-06-24 15:56:15</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>07:17:00</t>
+  </si>
+  <si>
+    <t>20:44:00</t>
+  </si>
+  <si>
+    <t>16:51:00</t>
+  </si>
+  <si>
+    <t>07:16:00</t>
+  </si>
+  <si>
+    <t>07:07:00</t>
+  </si>
+  <si>
+    <t>18:19:00</t>
+  </si>
+  <si>
+    <t>20:12:00</t>
+  </si>
+  <si>
+    <t>16:25:00</t>
+  </si>
+  <si>
+    <t>15:14:00</t>
+  </si>
+  <si>
+    <t>06:52:00</t>
+  </si>
+  <si>
+    <t>17:36:00</t>
+  </si>
+  <si>
+    <t>15:11:00</t>
+  </si>
+  <si>
+    <t>06:39:00</t>
+  </si>
+  <si>
+    <t>10:47:00</t>
+  </si>
+  <si>
+    <t>15:42:00</t>
+  </si>
+  <si>
+    <t>16:57:00</t>
+  </si>
+  <si>
+    <t>18:40:00</t>
+  </si>
+  <si>
+    <t>09:34:00</t>
+  </si>
+  <si>
+    <t>08:06:00</t>
+  </si>
+  <si>
+    <t>05:40:00</t>
+  </si>
+  <si>
+    <t>12:52:00</t>
+  </si>
+  <si>
+    <t>15:56:00</t>
+  </si>
+  <si>
+    <t>06:06:00</t>
+  </si>
+  <si>
+    <t>18:55:00</t>
+  </si>
+  <si>
+    <t>3232700578 3232700578</t>
+  </si>
+  <si>
+    <t>3232727318 3232727318</t>
+  </si>
+  <si>
+    <t>3232769075 3232769075</t>
+  </si>
+  <si>
+    <t>3232839696 3232839696</t>
+  </si>
+  <si>
+    <t>3232922575 3232922575</t>
+  </si>
+  <si>
+    <t>3233056026 3233056026</t>
+  </si>
+  <si>
+    <t>3233104495 3233104495</t>
+  </si>
+  <si>
+    <t>3233150437 3233150437</t>
+  </si>
+  <si>
+    <t>3233194541 3233194541</t>
+  </si>
+  <si>
+    <t>3233225370 3233225370</t>
+  </si>
+  <si>
+    <t>3233252226 3233252226</t>
+  </si>
+  <si>
+    <t>3233364863 3233364863</t>
+  </si>
+  <si>
+    <t>3233428023 3233428023</t>
+  </si>
+  <si>
+    <t>3233525009 3233525009</t>
+  </si>
+  <si>
+    <t>3233530638 3233530638</t>
+  </si>
+  <si>
+    <t>3233636760 3233636760</t>
+  </si>
+  <si>
+    <t>3233643381 3233643381</t>
+  </si>
+  <si>
+    <t>3233759538 3233759538</t>
+  </si>
+  <si>
+    <t>3233767878 3233767878</t>
+  </si>
+  <si>
+    <t>3233787457 3233787457</t>
+  </si>
+  <si>
+    <t>3233806927 3233806927</t>
+  </si>
+  <si>
+    <t>3233810805 3233810805</t>
+  </si>
+  <si>
+    <t>3233901333 3233901333</t>
+  </si>
+  <si>
+    <t>3234064328 3234064328</t>
+  </si>
+  <si>
+    <t>3234091276 3234091276</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДИЛЯНА-02 ЕООД</t>
@@ -608,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -617,14 +719,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -658,848 +763,1187 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>407.01</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2">
         <v>1.63</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>663.4299999999999</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.69</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>687.85</v>
       </c>
-      <c r="K2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>450</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3">
         <v>1.63</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>733.5</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.69</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>760.5</v>
       </c>
-      <c r="K3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F4">
         <v>60.22</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4">
         <v>1.62</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>97.56</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.69</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>101.77</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>350</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5">
         <v>1.6</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>560</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.66</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>581</v>
       </c>
-      <c r="K5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F6">
         <v>501.48</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6">
         <v>1.59</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>797.35</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.64</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>822.4299999999999</v>
       </c>
-      <c r="K6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F7">
         <v>409.8</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7">
         <v>1.59</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>651.58</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.64</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>672.0700000000001</v>
       </c>
-      <c r="K7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F8">
         <v>54.82</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8">
         <v>1.57</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>86.06999999999999</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.64</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>89.90000000000001</v>
       </c>
-      <c r="K8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F9">
         <v>470.86</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9">
         <v>1.57</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>739.25</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.63</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>767.5</v>
       </c>
-      <c r="K9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F10">
         <v>524.9400000000001</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10">
         <v>1.57</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>824.16</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.62</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>850.4</v>
       </c>
-      <c r="K10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>52</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F11">
         <v>421.03</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11">
         <v>1.57</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>661.02</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.61</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>677.86</v>
       </c>
-      <c r="K11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F12">
         <v>399.68</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12">
         <v>1.57</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>627.5</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.61</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>643.48</v>
       </c>
-      <c r="K12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F13">
         <v>385</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13">
         <v>1.57</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>604.45</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.6</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>616</v>
       </c>
-      <c r="K13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F14">
         <v>457.62</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14">
         <v>1.57</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>718.46</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.59</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>727.62</v>
       </c>
-      <c r="K14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F15">
         <v>459.04</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15">
         <v>1.56</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>716.1</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.58</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>725.28</v>
       </c>
-      <c r="K15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F16">
         <v>420</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16">
         <v>1.56</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>655.2</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.58</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>663.6</v>
       </c>
-      <c r="K16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F17">
         <v>532.53</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17">
         <v>1.51</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>804.12</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>1.54</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>820.1</v>
       </c>
-      <c r="K17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F18">
         <v>55.08</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18">
         <v>1.51</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>83.17</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.54</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>84.81999999999999</v>
       </c>
-      <c r="K18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" t="s">
+        <v>60</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19">
+        <v>550</v>
+      </c>
+      <c r="G19" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19">
+        <v>1.48</v>
+      </c>
+      <c r="I19" s="1">
+        <v>814</v>
+      </c>
+      <c r="J19">
+        <v>1.52</v>
+      </c>
+      <c r="K19" s="1">
+        <v>836</v>
+      </c>
+      <c r="L19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
         <v>27</v>
       </c>
-      <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20">
+        <v>58.78</v>
+      </c>
+      <c r="G20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20">
+        <v>1.48</v>
+      </c>
+      <c r="I20" s="1">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="J20">
+        <v>1.52</v>
+      </c>
+      <c r="K20" s="1">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="L20" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
         <v>34</v>
       </c>
-      <c r="E19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19">
-        <v>58.78</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H19">
-        <v>86.98999999999999</v>
-      </c>
-      <c r="I19" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J19">
-        <v>89.34999999999999</v>
-      </c>
-      <c r="K19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20">
-        <v>550</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H20">
-        <v>814</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J20">
-        <v>836</v>
-      </c>
-      <c r="K20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" t="s">
-        <v>28</v>
-      </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F21">
         <v>375.42</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21">
         <v>1.47</v>
       </c>
-      <c r="H21">
+      <c r="I21" s="1">
         <v>551.87</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21">
         <v>1.51</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="1">
         <v>566.88</v>
       </c>
-      <c r="K21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21" t="s">
+        <v>63</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F22">
         <v>462.3</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22">
         <v>1.47</v>
       </c>
-      <c r="H22">
+      <c r="I22" s="1">
         <v>679.58</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22">
         <v>1.51</v>
       </c>
-      <c r="J22">
+      <c r="K22" s="1">
         <v>698.0700000000001</v>
       </c>
-      <c r="K22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22" t="s">
+        <v>64</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F23">
         <v>380</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23">
         <v>1.47</v>
       </c>
-      <c r="H23">
+      <c r="I23" s="1">
         <v>558.6</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23">
         <v>1.51</v>
       </c>
-      <c r="J23">
+      <c r="K23" s="1">
         <v>573.8</v>
       </c>
-      <c r="K23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="6">
-        <v>8185.61</v>
-      </c>
-      <c r="C28" s="6">
-        <v>22</v>
-      </c>
-      <c r="D28" s="7">
-        <v>1.5532</v>
-      </c>
-      <c r="E28" s="6">
-        <v>12713.96</v>
-      </c>
-      <c r="F28" s="6">
-        <v>13056.28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="9">
-        <v>8185.61</v>
-      </c>
-      <c r="C29" s="9">
-        <v>22</v>
-      </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="9">
-        <v>12713.96</v>
-      </c>
-      <c r="F29" s="9">
-        <v>13056.28</v>
+      <c r="L23" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24">
+        <v>404.91</v>
+      </c>
+      <c r="G24" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24">
+        <v>1.45</v>
+      </c>
+      <c r="I24" s="1">
+        <v>587.12</v>
+      </c>
+      <c r="J24">
+        <v>1.51</v>
+      </c>
+      <c r="K24" s="1">
+        <v>611.41</v>
+      </c>
+      <c r="L24" t="s">
+        <v>66</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25">
+        <v>494.23</v>
+      </c>
+      <c r="G25" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25">
+        <v>1.44</v>
+      </c>
+      <c r="I25" s="1">
+        <v>711.6900000000001</v>
+      </c>
+      <c r="J25">
+        <v>1.51</v>
+      </c>
+      <c r="K25" s="1">
+        <v>746.29</v>
+      </c>
+      <c r="L25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26">
+        <v>430</v>
+      </c>
+      <c r="G26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26">
+        <v>1.44</v>
+      </c>
+      <c r="I26" s="1">
+        <v>619.2</v>
+      </c>
+      <c r="J26">
+        <v>1.51</v>
+      </c>
+      <c r="K26" s="1">
+        <v>649.3</v>
+      </c>
+      <c r="L26" t="s">
+        <v>48</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6">
+        <v>9514.75</v>
+      </c>
+      <c r="C31" s="6">
+        <v>25</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1.5378</v>
+      </c>
+      <c r="E31" s="6">
+        <v>14631.97</v>
+      </c>
+      <c r="F31" s="6">
+        <v>15063.28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="9">
+        <v>9514.75</v>
+      </c>
+      <c r="C32" s="9">
+        <v>25</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="9">
+        <v>14631.97</v>
+      </c>
+      <c r="F32" s="9">
+        <v>15063.28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="106">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -82,13 +88,46 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Стара Загора</t>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1908 О5 Стара Загора</t>
   </si>
   <si>
     <t>ТубаД</t>
@@ -118,43 +157,163 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-01 14:49:02</t>
-  </si>
-  <si>
-    <t>2026-07-02 16:33:57</t>
-  </si>
-  <si>
-    <t>2026-07-03 07:04:25</t>
-  </si>
-  <si>
-    <t>2026-07-03 15:51:50</t>
-  </si>
-  <si>
-    <t>2026-07-05 18:25:07</t>
-  </si>
-  <si>
-    <t>2026-07-07 18:16:04</t>
-  </si>
-  <si>
-    <t>2026-07-08 15:26:53</t>
-  </si>
-  <si>
-    <t>2026-07-10 09:01:34</t>
-  </si>
-  <si>
-    <t>2026-07-10 17:53:15</t>
-  </si>
-  <si>
-    <t>2026-07-10 19:24:53</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:19:54</t>
-  </si>
-  <si>
-    <t>2026-07-14 05:49:51</t>
-  </si>
-  <si>
-    <t>2026-07-15 14:56:25</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:49:00</t>
+  </si>
+  <si>
+    <t>16:33:00</t>
+  </si>
+  <si>
+    <t>07:04:00</t>
+  </si>
+  <si>
+    <t>15:52:00</t>
+  </si>
+  <si>
+    <t>18:25:00</t>
+  </si>
+  <si>
+    <t>18:16:00</t>
+  </si>
+  <si>
+    <t>15:26:00</t>
+  </si>
+  <si>
+    <t>17:53:00</t>
+  </si>
+  <si>
+    <t>09:01:00</t>
+  </si>
+  <si>
+    <t>19:24:00</t>
+  </si>
+  <si>
+    <t>20:19:00</t>
+  </si>
+  <si>
+    <t>05:50:00</t>
+  </si>
+  <si>
+    <t>14:56:00</t>
+  </si>
+  <si>
+    <t>17:29:00</t>
+  </si>
+  <si>
+    <t>07:33:00</t>
+  </si>
+  <si>
+    <t>16:44:00</t>
+  </si>
+  <si>
+    <t>06:12:00</t>
+  </si>
+  <si>
+    <t>09:20:00</t>
+  </si>
+  <si>
+    <t>09:53:00</t>
+  </si>
+  <si>
+    <t>03:21:00</t>
+  </si>
+  <si>
+    <t>19:23:00</t>
+  </si>
+  <si>
+    <t>18:19:00</t>
+  </si>
+  <si>
+    <t>06:43:00</t>
+  </si>
+  <si>
+    <t>17:57:00</t>
+  </si>
+  <si>
+    <t>15:48:00</t>
+  </si>
+  <si>
+    <t>16:01:00</t>
+  </si>
+  <si>
+    <t>3234168606 3234168606</t>
+  </si>
+  <si>
+    <t>3234201555 3234201555</t>
+  </si>
+  <si>
+    <t>3234206372 3234206372</t>
+  </si>
+  <si>
+    <t>3234250358 3234250358</t>
+  </si>
+  <si>
+    <t>3234360047 3234360047</t>
+  </si>
+  <si>
+    <t>3234442441 3234442441</t>
+  </si>
+  <si>
+    <t>3234464046 3234464046</t>
+  </si>
+  <si>
+    <t>3234564394 3234564394</t>
+  </si>
+  <si>
+    <t>3234607804 3234607804</t>
+  </si>
+  <si>
+    <t>3234615722 3234615722</t>
+  </si>
+  <si>
+    <t>3234651891 3234651891</t>
+  </si>
+  <si>
+    <t>3234764291 3234764291</t>
+  </si>
+  <si>
+    <t>3234835691 3234835691</t>
+  </si>
+  <si>
+    <t>3234947972 3234947972</t>
+  </si>
+  <si>
+    <t>3234971466 3234971466</t>
+  </si>
+  <si>
+    <t>3235098844 3235098844</t>
+  </si>
+  <si>
+    <t>3235210973 3235210973</t>
+  </si>
+  <si>
+    <t>3235262348 3235262348</t>
+  </si>
+  <si>
+    <t>3235337945 3235337945</t>
+  </si>
+  <si>
+    <t>3235424570 3235424570</t>
+  </si>
+  <si>
+    <t>3235440298 3235440298</t>
+  </si>
+  <si>
+    <t>3235501013 3235501013</t>
+  </si>
+  <si>
+    <t>3235523032 3235523032</t>
+  </si>
+  <si>
+    <t>3235531593 3235531593</t>
+  </si>
+  <si>
+    <t>3235584402 3235584402</t>
+  </si>
+  <si>
+    <t>3235639233 3235639233</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДИЛЯНА-02 ЕООД</t>
@@ -572,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -581,15 +740,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -626,572 +787,1228 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F2">
         <v>58.53</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2">
         <v>1.44</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>84.28</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>88.38</v>
       </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="L2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F3">
         <v>400</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3">
         <v>1.44</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>576</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.51</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>604</v>
       </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F4">
         <v>460.3</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4">
         <v>1.44</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>662.83</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.51</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>695.05</v>
       </c>
-      <c r="K4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="L4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F5">
         <v>550</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5">
         <v>1.44</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>792</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.51</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>830.5</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
         <v>37</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <v>56.26</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6">
         <v>1.45</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>81.58</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.52</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>85.52</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>38</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>22.18</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7">
         <v>1.45</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>32.16</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.52</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>33.71</v>
       </c>
-      <c r="K7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="L7" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F8">
         <v>519.03</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8">
         <v>1.45</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>752.59</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.52</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>788.9299999999999</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9">
+        <v>493.66</v>
+      </c>
+      <c r="G9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9">
+        <v>1.48</v>
+      </c>
+      <c r="I9" s="1">
+        <v>730.62</v>
+      </c>
+      <c r="J9">
+        <v>1.54</v>
+      </c>
+      <c r="K9" s="1">
+        <v>760.24</v>
+      </c>
+      <c r="L9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
         <v>40</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9">
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10">
         <v>458.49</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10">
         <v>1.48</v>
       </c>
-      <c r="H9">
+      <c r="I10" s="1">
         <v>678.5700000000001</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J10">
         <v>1.54</v>
       </c>
-      <c r="J9">
+      <c r="K10" s="1">
         <v>706.0700000000001</v>
       </c>
-      <c r="K9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10">
-        <v>493.66</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H10">
-        <v>730.62</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="J10">
-        <v>760.24</v>
-      </c>
-      <c r="K10" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="L10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F11">
         <v>375</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11">
         <v>1.48</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>555</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.54</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>577.5</v>
       </c>
-      <c r="K11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="L11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F12">
         <v>59.59</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12">
         <v>1.48</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>88.19</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.54</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>91.77</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
         <v>44</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F13">
         <v>395.53</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13">
         <v>1.51</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>597.25</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.56</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>617.03</v>
       </c>
-      <c r="K13" t="s">
-        <v>45</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="L13" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F14">
         <v>345.84</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14">
         <v>1.53</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>529.14</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.58</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>546.4299999999999</v>
       </c>
-      <c r="K14" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="5" t="s">
+      <c r="L14" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15">
+        <v>473.35</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15">
+        <v>1.54</v>
+      </c>
+      <c r="I15" s="1">
+        <v>728.96</v>
+      </c>
+      <c r="J15">
+        <v>1.63</v>
+      </c>
+      <c r="K15" s="1">
+        <v>771.5599999999999</v>
+      </c>
+      <c r="L15" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16">
+        <v>441.24</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16">
+        <v>1.57</v>
+      </c>
+      <c r="I16" s="1">
+        <v>692.75</v>
+      </c>
+      <c r="J16">
+        <v>1.65</v>
+      </c>
+      <c r="K16" s="1">
+        <v>728.05</v>
+      </c>
+      <c r="L16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17">
+        <v>404.88</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17">
+        <v>1.58</v>
+      </c>
+      <c r="I17" s="1">
+        <v>639.71</v>
+      </c>
+      <c r="J17">
+        <v>1.68</v>
+      </c>
+      <c r="K17" s="1">
+        <v>680.2</v>
+      </c>
+      <c r="L17" t="s">
+        <v>63</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18">
+        <v>496.56</v>
+      </c>
+      <c r="G18" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18">
+        <v>1.62</v>
+      </c>
+      <c r="I18" s="1">
+        <v>804.4299999999999</v>
+      </c>
+      <c r="J18">
+        <v>1.7</v>
+      </c>
+      <c r="K18" s="1">
+        <v>844.15</v>
+      </c>
+      <c r="L18" t="s">
+        <v>64</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19">
+        <v>425.49</v>
+      </c>
+      <c r="G19" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19">
+        <v>1.65</v>
+      </c>
+      <c r="I19" s="1">
+        <v>702.0599999999999</v>
+      </c>
+      <c r="J19">
+        <v>1.72</v>
+      </c>
+      <c r="K19" s="1">
+        <v>731.84</v>
+      </c>
+      <c r="L19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20">
+        <v>384.87</v>
+      </c>
+      <c r="G20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20">
+        <v>1.65</v>
+      </c>
+      <c r="I20" s="1">
+        <v>635.04</v>
+      </c>
+      <c r="J20">
+        <v>1.74</v>
+      </c>
+      <c r="K20" s="1">
+        <v>669.67</v>
+      </c>
+      <c r="L20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21">
+        <v>335</v>
+      </c>
+      <c r="G21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21">
+        <v>1.65</v>
+      </c>
+      <c r="I21" s="1">
+        <v>552.75</v>
+      </c>
+      <c r="J21">
+        <v>1.75</v>
+      </c>
+      <c r="K21" s="1">
+        <v>586.25</v>
+      </c>
+      <c r="L21" t="s">
+        <v>67</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22">
+        <v>525.55</v>
+      </c>
+      <c r="G22" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22">
+        <v>1.65</v>
+      </c>
+      <c r="I22" s="1">
+        <v>867.16</v>
+      </c>
+      <c r="J22">
+        <v>1.75</v>
+      </c>
+      <c r="K22" s="1">
+        <v>919.71</v>
+      </c>
+      <c r="L22" t="s">
+        <v>68</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23">
+        <v>54.33</v>
+      </c>
+      <c r="G23" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23">
+        <v>1.68</v>
+      </c>
+      <c r="I23" s="1">
+        <v>91.27</v>
+      </c>
+      <c r="J23">
+        <v>1.75</v>
+      </c>
+      <c r="K23" s="1">
+        <v>95.08</v>
+      </c>
+      <c r="L23" t="s">
+        <v>69</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24">
+        <v>470</v>
+      </c>
+      <c r="G24" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24">
+        <v>1.7</v>
+      </c>
+      <c r="I24" s="1">
+        <v>799</v>
+      </c>
+      <c r="J24">
+        <v>1.75</v>
+      </c>
+      <c r="K24" s="1">
+        <v>822.5</v>
+      </c>
+      <c r="L24" t="s">
+        <v>70</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25">
+        <v>513.1799999999999</v>
+      </c>
+      <c r="G25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25">
+        <v>1.7</v>
+      </c>
+      <c r="I25" s="1">
+        <v>872.41</v>
+      </c>
+      <c r="J25">
+        <v>1.75</v>
+      </c>
+      <c r="K25" s="1">
+        <v>898.0599999999999</v>
+      </c>
+      <c r="L25" t="s">
+        <v>71</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="6">
-        <v>4194.41</v>
-      </c>
-      <c r="C19" s="6">
-        <v>13</v>
-      </c>
-      <c r="D19" s="7">
-        <v>1.4687</v>
-      </c>
-      <c r="E19" s="6">
-        <v>6160.21</v>
-      </c>
-      <c r="F19" s="6">
-        <v>6425.13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="9">
-        <v>4194.41</v>
-      </c>
-      <c r="C20" s="9">
-        <v>13</v>
-      </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="9">
-        <v>6160.21</v>
-      </c>
-      <c r="F20" s="9">
-        <v>6425.13</v>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26">
+        <v>385.01</v>
+      </c>
+      <c r="G26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26">
+        <v>1.7</v>
+      </c>
+      <c r="I26" s="1">
+        <v>654.52</v>
+      </c>
+      <c r="J26">
+        <v>1.76</v>
+      </c>
+      <c r="K26" s="1">
+        <v>677.62</v>
+      </c>
+      <c r="L26" t="s">
+        <v>72</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27">
+        <v>462.5</v>
+      </c>
+      <c r="G27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27">
+        <v>1.72</v>
+      </c>
+      <c r="I27" s="1">
+        <v>795.5</v>
+      </c>
+      <c r="J27">
+        <v>1.77</v>
+      </c>
+      <c r="K27" s="1">
+        <v>818.62</v>
+      </c>
+      <c r="L27" t="s">
+        <v>73</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="6">
+        <v>9566.370000000001</v>
+      </c>
+      <c r="C32" s="6">
+        <v>26</v>
+      </c>
+      <c r="D32" s="7">
+        <v>1.5676</v>
+      </c>
+      <c r="E32" s="6">
+        <v>14995.77</v>
+      </c>
+      <c r="F32" s="6">
+        <v>15668.44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="9">
+        <v>9566.370000000001</v>
+      </c>
+      <c r="C33" s="9">
+        <v>26</v>
+      </c>
+      <c r="D33" s="7"/>
+      <c r="E33" s="9">
+        <v>14995.77</v>
+      </c>
+      <c r="F33" s="9">
+        <v>15668.44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
@@ -340,7 +340,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1979,7 +1979,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="7">
-        <v>1.5676</v>
+        <v>1.567551</v>
       </c>
       <c r="E32" s="6">
         <v>14995.77</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="107">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -731,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -744,13 +747,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -793,1154 +796,1235 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F2">
         <v>58.53</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2">
-        <v>1.44</v>
+        <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>84.28</v>
+        <v>1.439</v>
       </c>
       <c r="J2">
+        <v>84.22467</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.51</v>
       </c>
-      <c r="K2" s="1">
-        <v>88.38</v>
-      </c>
-      <c r="L2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="L2" s="1">
+        <v>88.38030000000001</v>
+      </c>
+      <c r="M2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3">
         <v>400</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H3">
-        <v>1.44</v>
+        <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>576</v>
+        <v>1.439</v>
       </c>
       <c r="J3">
+        <v>575.6</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.51</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>604</v>
       </c>
-      <c r="L3" t="s">
-        <v>49</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="M3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4">
+        <v>460.298</v>
+      </c>
+      <c r="G4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4">
+        <v>1.399</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.439</v>
+      </c>
+      <c r="J4">
+        <v>662.368822</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="L4" s="1">
+        <v>695.04998</v>
+      </c>
+      <c r="M4" t="s">
+        <v>51</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>44</v>
       </c>
-      <c r="E4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4">
-        <v>460.3</v>
-      </c>
-      <c r="G4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4">
-        <v>1.44</v>
-      </c>
-      <c r="I4" s="1">
-        <v>662.83</v>
-      </c>
-      <c r="J4">
-        <v>1.51</v>
-      </c>
-      <c r="K4" s="1">
-        <v>695.05</v>
-      </c>
-      <c r="L4" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" t="s">
-        <v>43</v>
-      </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F5">
         <v>550</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5">
-        <v>1.44</v>
+        <v>1.399</v>
       </c>
       <c r="I5" s="1">
-        <v>792</v>
+        <v>1.439</v>
       </c>
       <c r="J5">
+        <v>791.45</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.51</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>830.5</v>
       </c>
-      <c r="L5" t="s">
-        <v>51</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="M5" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6">
+        <v>56.263</v>
+      </c>
+      <c r="G6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6">
+        <v>1.406</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.446</v>
+      </c>
+      <c r="J6">
+        <v>81.356298</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L6" s="1">
+        <v>85.51976000000001</v>
+      </c>
+      <c r="M6" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7">
+        <v>22.178</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7">
+        <v>1.406</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.446</v>
+      </c>
+      <c r="J7">
+        <v>32.069388</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L7" s="1">
+        <v>33.71056</v>
+      </c>
+      <c r="M7" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8">
+        <v>519.033</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8">
+        <v>1.412</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.452</v>
+      </c>
+      <c r="J8">
+        <v>753.635916</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L8" s="1">
+        <v>788.93016</v>
+      </c>
+      <c r="M8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
         <v>42</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D9" t="s">
         <v>46</v>
       </c>
-      <c r="F6">
-        <v>56.26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6">
-        <v>1.45</v>
-      </c>
-      <c r="I6" s="1">
-        <v>81.58</v>
-      </c>
-      <c r="J6">
-        <v>1.52</v>
-      </c>
-      <c r="K6" s="1">
-        <v>85.52</v>
-      </c>
-      <c r="L6" t="s">
-        <v>52</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7">
-        <v>22.18</v>
-      </c>
-      <c r="G7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7">
-        <v>1.45</v>
-      </c>
-      <c r="I7" s="1">
-        <v>32.16</v>
-      </c>
-      <c r="J7">
-        <v>1.52</v>
-      </c>
-      <c r="K7" s="1">
-        <v>33.71</v>
-      </c>
-      <c r="L7" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8">
-        <v>519.03</v>
-      </c>
-      <c r="G8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8">
-        <v>1.45</v>
-      </c>
-      <c r="I8" s="1">
-        <v>752.59</v>
-      </c>
-      <c r="J8">
-        <v>1.52</v>
-      </c>
-      <c r="K8" s="1">
-        <v>788.9299999999999</v>
-      </c>
-      <c r="L8" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9">
+        <v>493.662</v>
+      </c>
+      <c r="G9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9">
+        <v>1.437</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.477</v>
+      </c>
+      <c r="J9">
+        <v>729.138774</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L9" s="1">
+        <v>760.23948</v>
+      </c>
+      <c r="M9" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
         <v>41</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9">
-        <v>493.66</v>
-      </c>
-      <c r="G9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9">
-        <v>1.48</v>
-      </c>
-      <c r="I9" s="1">
-        <v>730.62</v>
-      </c>
-      <c r="J9">
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10">
+        <v>458.487</v>
+      </c>
+      <c r="G10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10">
+        <v>1.437</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.477</v>
+      </c>
+      <c r="J10">
+        <v>677.185299</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.54</v>
       </c>
-      <c r="K9" s="1">
-        <v>760.24</v>
-      </c>
-      <c r="L9" t="s">
-        <v>55</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="L10" s="1">
+        <v>706.06998</v>
+      </c>
+      <c r="M10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
         <v>40</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>44</v>
       </c>
-      <c r="E10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10">
-        <v>458.49</v>
-      </c>
-      <c r="G10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10">
-        <v>1.48</v>
-      </c>
-      <c r="I10" s="1">
-        <v>678.5700000000001</v>
-      </c>
-      <c r="J10">
-        <v>1.54</v>
-      </c>
-      <c r="K10" s="1">
-        <v>706.0700000000001</v>
-      </c>
-      <c r="L10" t="s">
-        <v>56</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
-      </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F11">
         <v>375</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H11">
-        <v>1.48</v>
+        <v>1.437</v>
       </c>
       <c r="I11" s="1">
-        <v>555</v>
+        <v>1.477</v>
       </c>
       <c r="J11">
+        <v>553.875</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.54</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>577.5</v>
       </c>
-      <c r="L11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="M11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12">
+        <v>59.591</v>
+      </c>
+      <c r="G12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12">
+        <v>1.437</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.477</v>
+      </c>
+      <c r="J12">
+        <v>88.015907</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L12" s="1">
+        <v>91.77014</v>
+      </c>
+      <c r="M12" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13">
+        <v>395.532</v>
+      </c>
+      <c r="G13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13">
+        <v>1.469</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1.509</v>
+      </c>
+      <c r="J13">
+        <v>596.857788</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L13" s="1">
+        <v>617.0299199999999</v>
+      </c>
+      <c r="M13" t="s">
+        <v>60</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14">
+        <v>345.842</v>
+      </c>
+      <c r="G14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14">
+        <v>1.489</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1.529</v>
+      </c>
+      <c r="J14">
+        <v>528.792418</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="L14" s="1">
+        <v>546.43036</v>
+      </c>
+      <c r="M14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
         <v>42</v>
       </c>
-      <c r="E12" t="s">
+      <c r="D15" t="s">
         <v>46</v>
       </c>
-      <c r="F12">
-        <v>59.59</v>
-      </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12">
-        <v>1.48</v>
-      </c>
-      <c r="I12" s="1">
-        <v>88.19</v>
-      </c>
-      <c r="J12">
-        <v>1.54</v>
-      </c>
-      <c r="K12" s="1">
-        <v>91.77</v>
-      </c>
-      <c r="L12" t="s">
-        <v>58</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13">
-        <v>395.53</v>
-      </c>
-      <c r="G13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13">
-        <v>1.51</v>
-      </c>
-      <c r="I13" s="1">
-        <v>597.25</v>
-      </c>
-      <c r="J13">
-        <v>1.56</v>
-      </c>
-      <c r="K13" s="1">
-        <v>617.03</v>
-      </c>
-      <c r="L13" t="s">
-        <v>59</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14">
-        <v>345.84</v>
-      </c>
-      <c r="G14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14">
-        <v>1.53</v>
-      </c>
-      <c r="I14" s="1">
-        <v>529.14</v>
-      </c>
-      <c r="J14">
-        <v>1.58</v>
-      </c>
-      <c r="K14" s="1">
-        <v>546.4299999999999</v>
-      </c>
-      <c r="L14" t="s">
-        <v>60</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F15">
         <v>473.35</v>
       </c>
       <c r="G15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H15">
-        <v>1.54</v>
+        <v>1.499</v>
       </c>
       <c r="I15" s="1">
-        <v>728.96</v>
+        <v>1.539</v>
       </c>
       <c r="J15">
+        <v>728.48565</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.63</v>
       </c>
-      <c r="K15" s="1">
-        <v>771.5599999999999</v>
-      </c>
-      <c r="L15" t="s">
-        <v>61</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="L15" s="1">
+        <v>771.5605</v>
+      </c>
+      <c r="M15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16">
+        <v>441.242</v>
+      </c>
+      <c r="G16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16">
+        <v>1.528</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1.568</v>
+      </c>
+      <c r="J16">
+        <v>691.8674559999999</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1.65</v>
+      </c>
+      <c r="L16" s="1">
+        <v>728.0493</v>
+      </c>
+      <c r="M16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17">
+        <v>404.881</v>
+      </c>
+      <c r="G17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17">
+        <v>1.546</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1.576</v>
+      </c>
+      <c r="J17">
+        <v>638.092456</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L17" s="1">
+        <v>680.20008</v>
+      </c>
+      <c r="M17" t="s">
+        <v>64</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18">
+        <v>496.559</v>
+      </c>
+      <c r="G18" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18">
+        <v>1.588</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1.618</v>
+      </c>
+      <c r="J18">
+        <v>803.432462</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L18" s="1">
+        <v>844.1503</v>
+      </c>
+      <c r="M18" t="s">
+        <v>65</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19">
+        <v>425.488</v>
+      </c>
+      <c r="G19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19">
+        <v>1.619</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1.649</v>
+      </c>
+      <c r="J19">
+        <v>701.629712</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1.72</v>
+      </c>
+      <c r="L19" s="1">
+        <v>731.8393600000001</v>
+      </c>
+      <c r="M19" t="s">
+        <v>66</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20">
+        <v>384.868</v>
+      </c>
+      <c r="G20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20">
+        <v>1.619</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1.649</v>
+      </c>
+      <c r="J20">
+        <v>634.647332</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="L20" s="1">
+        <v>669.6703199999999</v>
+      </c>
+      <c r="M20" t="s">
+        <v>67</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
         <v>40</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D21" t="s">
         <v>44</v>
       </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16">
-        <v>441.24</v>
-      </c>
-      <c r="G16" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16">
-        <v>1.57</v>
-      </c>
-      <c r="I16" s="1">
-        <v>692.75</v>
-      </c>
-      <c r="J16">
-        <v>1.65</v>
-      </c>
-      <c r="K16" s="1">
-        <v>728.05</v>
-      </c>
-      <c r="L16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17">
-        <v>404.88</v>
-      </c>
-      <c r="G17" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17">
-        <v>1.58</v>
-      </c>
-      <c r="I17" s="1">
-        <v>639.71</v>
-      </c>
-      <c r="J17">
-        <v>1.68</v>
-      </c>
-      <c r="K17" s="1">
-        <v>680.2</v>
-      </c>
-      <c r="L17" t="s">
-        <v>63</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18">
-        <v>496.56</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
-      </c>
-      <c r="H18">
-        <v>1.62</v>
-      </c>
-      <c r="I18" s="1">
-        <v>804.4299999999999</v>
-      </c>
-      <c r="J18">
-        <v>1.7</v>
-      </c>
-      <c r="K18" s="1">
-        <v>844.15</v>
-      </c>
-      <c r="L18" t="s">
-        <v>64</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19">
-        <v>425.49</v>
-      </c>
-      <c r="G19" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19">
-        <v>1.65</v>
-      </c>
-      <c r="I19" s="1">
-        <v>702.0599999999999</v>
-      </c>
-      <c r="J19">
-        <v>1.72</v>
-      </c>
-      <c r="K19" s="1">
-        <v>731.84</v>
-      </c>
-      <c r="L19" t="s">
-        <v>65</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20">
-        <v>384.87</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20">
-        <v>1.65</v>
-      </c>
-      <c r="I20" s="1">
-        <v>635.04</v>
-      </c>
-      <c r="J20">
-        <v>1.74</v>
-      </c>
-      <c r="K20" s="1">
-        <v>669.67</v>
-      </c>
-      <c r="L20" t="s">
-        <v>66</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" t="s">
-        <v>43</v>
-      </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F21">
         <v>335</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H21">
-        <v>1.65</v>
+        <v>1.619</v>
       </c>
       <c r="I21" s="1">
-        <v>552.75</v>
+        <v>1.649</v>
       </c>
       <c r="J21">
+        <v>552.415</v>
+      </c>
+      <c r="K21" s="1">
         <v>1.75</v>
       </c>
-      <c r="K21" s="1">
+      <c r="L21" s="1">
         <v>586.25</v>
       </c>
-      <c r="L21" t="s">
-        <v>67</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="M21" t="s">
+        <v>68</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22">
+        <v>525.549</v>
+      </c>
+      <c r="G22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22">
+        <v>1.619</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1.649</v>
+      </c>
+      <c r="J22">
+        <v>866.630301</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L22" s="1">
+        <v>919.71075</v>
+      </c>
+      <c r="M22" t="s">
+        <v>69</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" t="s">
         <v>36</v>
       </c>
-      <c r="C22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22">
-        <v>525.55</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
-      </c>
-      <c r="H22">
-        <v>1.65</v>
-      </c>
-      <c r="I22" s="1">
-        <v>867.16</v>
-      </c>
-      <c r="J22">
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23">
+        <v>54.331</v>
+      </c>
+      <c r="G23" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23">
+        <v>1.653</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1.683</v>
+      </c>
+      <c r="J23">
+        <v>91.43907299999999</v>
+      </c>
+      <c r="K23" s="1">
         <v>1.75</v>
       </c>
-      <c r="K22" s="1">
-        <v>919.71</v>
-      </c>
-      <c r="L22" t="s">
-        <v>68</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23">
-        <v>54.33</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
-      </c>
-      <c r="H23">
-        <v>1.68</v>
-      </c>
-      <c r="I23" s="1">
-        <v>91.27</v>
-      </c>
-      <c r="J23">
-        <v>1.75</v>
-      </c>
-      <c r="K23" s="1">
-        <v>95.08</v>
-      </c>
-      <c r="L23" t="s">
-        <v>69</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="L23" s="1">
+        <v>95.07925</v>
+      </c>
+      <c r="M23" t="s">
+        <v>70</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F24">
         <v>470</v>
       </c>
       <c r="G24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H24">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I24" s="1">
-        <v>799</v>
+        <v>1.704</v>
       </c>
       <c r="J24">
+        <v>800.88</v>
+      </c>
+      <c r="K24" s="1">
         <v>1.75</v>
       </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
         <v>822.5</v>
       </c>
-      <c r="L24" t="s">
-        <v>70</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="M24" t="s">
+        <v>71</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25">
+        <v>513.183</v>
+      </c>
+      <c r="G25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25">
+        <v>1.674</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1.704</v>
+      </c>
+      <c r="J25">
+        <v>874.463832</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L25" s="1">
+        <v>898.07025</v>
+      </c>
+      <c r="M25" t="s">
+        <v>72</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" t="s">
         <v>40</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>44</v>
       </c>
-      <c r="E25" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25">
-        <v>513.1799999999999</v>
-      </c>
-      <c r="G25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H25">
-        <v>1.7</v>
-      </c>
-      <c r="I25" s="1">
-        <v>872.41</v>
-      </c>
-      <c r="J25">
-        <v>1.75</v>
-      </c>
-      <c r="K25" s="1">
-        <v>898.0599999999999</v>
-      </c>
-      <c r="L25" t="s">
-        <v>71</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" t="s">
-        <v>43</v>
-      </c>
       <c r="E26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F26">
-        <v>385.01</v>
+        <v>385.011</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H26">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I26" s="1">
-        <v>654.52</v>
+        <v>1.704</v>
       </c>
       <c r="J26">
+        <v>656.058744</v>
+      </c>
+      <c r="K26" s="1">
         <v>1.76</v>
       </c>
-      <c r="K26" s="1">
-        <v>677.62</v>
-      </c>
-      <c r="L26" t="s">
-        <v>72</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="L26" s="1">
+        <v>677.61936</v>
+      </c>
+      <c r="M26" t="s">
+        <v>73</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F27">
-        <v>462.5</v>
+        <v>462.503</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H27">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I27" s="1">
-        <v>795.5</v>
+        <v>1.719</v>
       </c>
       <c r="J27">
+        <v>795.042657</v>
+      </c>
+      <c r="K27" s="1">
         <v>1.77</v>
       </c>
-      <c r="K27" s="1">
-        <v>818.62</v>
-      </c>
-      <c r="L27" t="s">
-        <v>73</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="L27" s="1">
+        <v>818.63031</v>
+      </c>
+      <c r="M27" t="s">
+        <v>74</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -1948,62 +2032,62 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:15">
       <c r="A31" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B32" s="6">
-        <v>9566.370000000001</v>
+        <v>9566.380999999999</v>
       </c>
       <c r="C32" s="6">
         <v>26</v>
       </c>
       <c r="D32" s="7">
-        <v>1.567551</v>
+        <v>1.56691</v>
       </c>
       <c r="E32" s="6">
-        <v>14995.77</v>
+        <v>14989.65</v>
       </c>
       <c r="F32" s="6">
-        <v>15668.44</v>
+        <v>15668.46</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B33" s="9">
-        <v>9566.370000000001</v>
+        <v>9566.380999999999</v>
       </c>
       <c r="C33" s="9">
         <v>26</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="9">
-        <v>14995.77</v>
+        <v>14989.65</v>
       </c>
       <c r="F33" s="9">
-        <v>15668.44</v>
+        <v>15668.46</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИЛЯНА-02 ЕООД/ДИЛЯНА-02 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="106">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -342,8 +339,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -436,10 +433,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -734,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -747,13 +744,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -796,1235 +793,1154 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2">
         <v>58.53</v>
       </c>
       <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2">
+        <v>1.439</v>
+      </c>
+      <c r="I2" s="1">
+        <v>84.22499999999999</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>88.38</v>
+      </c>
+      <c r="L2" t="s">
         <v>48</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.439</v>
-      </c>
-      <c r="J2">
-        <v>84.22467</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>88.38030000000001</v>
-      </c>
-      <c r="M2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3">
         <v>400</v>
       </c>
       <c r="G3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H3">
-        <v>1.399</v>
+        <v>1.439</v>
       </c>
       <c r="I3" s="1">
-        <v>1.439</v>
+        <v>575.6</v>
       </c>
       <c r="J3">
-        <v>575.6</v>
+        <v>1.51</v>
       </c>
       <c r="K3" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L3" s="1">
         <v>604</v>
       </c>
-      <c r="M3" t="s">
-        <v>50</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="L3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F4">
         <v>460.298</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H4">
-        <v>1.399</v>
+        <v>1.439</v>
       </c>
       <c r="I4" s="1">
-        <v>1.439</v>
+        <v>662.369</v>
       </c>
       <c r="J4">
-        <v>662.368822</v>
+        <v>1.51</v>
       </c>
       <c r="K4" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L4" s="1">
-        <v>695.04998</v>
-      </c>
-      <c r="M4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>695.05</v>
+      </c>
+      <c r="L4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5">
         <v>550</v>
       </c>
       <c r="G5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H5">
-        <v>1.399</v>
+        <v>1.439</v>
       </c>
       <c r="I5" s="1">
-        <v>1.439</v>
+        <v>791.45</v>
       </c>
       <c r="J5">
-        <v>791.45</v>
+        <v>1.51</v>
       </c>
       <c r="K5" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L5" s="1">
         <v>830.5</v>
       </c>
-      <c r="M5" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="L5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
         <v>38</v>
       </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <v>56.263</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H6">
-        <v>1.406</v>
+        <v>1.446</v>
       </c>
       <c r="I6" s="1">
-        <v>1.446</v>
+        <v>81.35599999999999</v>
       </c>
       <c r="J6">
-        <v>81.356298</v>
+        <v>1.52</v>
       </c>
       <c r="K6" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L6" s="1">
-        <v>85.51976000000001</v>
-      </c>
-      <c r="M6" t="s">
-        <v>53</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>85.52</v>
+      </c>
+      <c r="L6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>22.178</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H7">
-        <v>1.406</v>
+        <v>1.446</v>
       </c>
       <c r="I7" s="1">
-        <v>1.446</v>
+        <v>32.069</v>
       </c>
       <c r="J7">
-        <v>32.069388</v>
+        <v>1.52</v>
       </c>
       <c r="K7" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L7" s="1">
-        <v>33.71056</v>
-      </c>
-      <c r="M7" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>33.711</v>
+      </c>
+      <c r="L7" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8">
         <v>519.033</v>
       </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H8">
-        <v>1.412</v>
+        <v>1.452</v>
       </c>
       <c r="I8" s="1">
-        <v>1.452</v>
+        <v>753.636</v>
       </c>
       <c r="J8">
-        <v>753.635916</v>
+        <v>1.52</v>
       </c>
       <c r="K8" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L8" s="1">
-        <v>788.93016</v>
-      </c>
-      <c r="M8" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>788.9299999999999</v>
+      </c>
+      <c r="L8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9">
         <v>493.662</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H9">
-        <v>1.437</v>
+        <v>1.477</v>
       </c>
       <c r="I9" s="1">
-        <v>1.477</v>
+        <v>729.139</v>
       </c>
       <c r="J9">
-        <v>729.138774</v>
+        <v>1.54</v>
       </c>
       <c r="K9" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L9" s="1">
-        <v>760.23948</v>
-      </c>
-      <c r="M9" t="s">
-        <v>56</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>760.239</v>
+      </c>
+      <c r="L9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F10">
         <v>458.487</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H10">
-        <v>1.437</v>
+        <v>1.477</v>
       </c>
       <c r="I10" s="1">
-        <v>1.477</v>
+        <v>677.1849999999999</v>
       </c>
       <c r="J10">
-        <v>677.185299</v>
+        <v>1.54</v>
       </c>
       <c r="K10" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L10" s="1">
-        <v>706.06998</v>
-      </c>
-      <c r="M10" t="s">
-        <v>57</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>706.0700000000001</v>
+      </c>
+      <c r="L10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11">
         <v>375</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H11">
-        <v>1.437</v>
+        <v>1.477</v>
       </c>
       <c r="I11" s="1">
-        <v>1.477</v>
+        <v>553.875</v>
       </c>
       <c r="J11">
-        <v>553.875</v>
+        <v>1.54</v>
       </c>
       <c r="K11" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L11" s="1">
         <v>577.5</v>
       </c>
-      <c r="M11" t="s">
-        <v>58</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="L11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12">
         <v>59.591</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H12">
-        <v>1.437</v>
+        <v>1.477</v>
       </c>
       <c r="I12" s="1">
-        <v>1.477</v>
+        <v>88.01600000000001</v>
       </c>
       <c r="J12">
-        <v>88.015907</v>
+        <v>1.54</v>
       </c>
       <c r="K12" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L12" s="1">
-        <v>91.77014</v>
-      </c>
-      <c r="M12" t="s">
-        <v>59</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>91.77</v>
+      </c>
+      <c r="L12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13">
         <v>395.532</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H13">
-        <v>1.469</v>
+        <v>1.509</v>
       </c>
       <c r="I13" s="1">
-        <v>1.509</v>
+        <v>596.8579999999999</v>
       </c>
       <c r="J13">
-        <v>596.857788</v>
+        <v>1.56</v>
       </c>
       <c r="K13" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L13" s="1">
-        <v>617.0299199999999</v>
-      </c>
-      <c r="M13" t="s">
-        <v>60</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>617.03</v>
+      </c>
+      <c r="L13" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F14">
         <v>345.842</v>
       </c>
       <c r="G14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H14">
-        <v>1.489</v>
+        <v>1.529</v>
       </c>
       <c r="I14" s="1">
-        <v>1.529</v>
+        <v>528.792</v>
       </c>
       <c r="J14">
-        <v>528.792418</v>
+        <v>1.58</v>
       </c>
       <c r="K14" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L14" s="1">
-        <v>546.43036</v>
-      </c>
-      <c r="M14" t="s">
-        <v>61</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>546.4299999999999</v>
+      </c>
+      <c r="L14" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15">
         <v>473.35</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H15">
-        <v>1.499</v>
+        <v>1.539</v>
       </c>
       <c r="I15" s="1">
-        <v>1.539</v>
+        <v>728.486</v>
       </c>
       <c r="J15">
-        <v>728.48565</v>
+        <v>1.63</v>
       </c>
       <c r="K15" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L15" s="1">
-        <v>771.5605</v>
-      </c>
-      <c r="M15" t="s">
-        <v>62</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>771.5599999999999</v>
+      </c>
+      <c r="L15" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F16">
         <v>441.242</v>
       </c>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H16">
-        <v>1.528</v>
+        <v>1.568</v>
       </c>
       <c r="I16" s="1">
-        <v>1.568</v>
+        <v>691.867</v>
       </c>
       <c r="J16">
-        <v>691.8674559999999</v>
+        <v>1.65</v>
       </c>
       <c r="K16" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="L16" s="1">
-        <v>728.0493</v>
-      </c>
-      <c r="M16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>728.049</v>
+      </c>
+      <c r="L16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17">
         <v>404.881</v>
       </c>
       <c r="G17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H17">
-        <v>1.546</v>
+        <v>1.576</v>
       </c>
       <c r="I17" s="1">
-        <v>1.576</v>
+        <v>638.092</v>
       </c>
       <c r="J17">
-        <v>638.092456</v>
+        <v>1.68</v>
       </c>
       <c r="K17" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L17" s="1">
-        <v>680.20008</v>
-      </c>
-      <c r="M17" t="s">
-        <v>64</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>680.2</v>
+      </c>
+      <c r="L17" t="s">
+        <v>63</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18">
         <v>496.559</v>
       </c>
       <c r="G18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H18">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I18" s="1">
-        <v>1.618</v>
+        <v>803.432</v>
       </c>
       <c r="J18">
-        <v>803.432462</v>
+        <v>1.7</v>
       </c>
       <c r="K18" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L18" s="1">
-        <v>844.1503</v>
-      </c>
-      <c r="M18" t="s">
-        <v>65</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>844.15</v>
+      </c>
+      <c r="L18" t="s">
+        <v>64</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F19">
         <v>425.488</v>
       </c>
       <c r="G19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H19">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I19" s="1">
-        <v>1.649</v>
+        <v>701.63</v>
       </c>
       <c r="J19">
-        <v>701.629712</v>
+        <v>1.72</v>
       </c>
       <c r="K19" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L19" s="1">
-        <v>731.8393600000001</v>
-      </c>
-      <c r="M19" t="s">
-        <v>66</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>731.8390000000001</v>
+      </c>
+      <c r="L19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F20">
         <v>384.868</v>
       </c>
       <c r="G20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H20">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I20" s="1">
-        <v>1.649</v>
+        <v>634.647</v>
       </c>
       <c r="J20">
-        <v>634.647332</v>
+        <v>1.74</v>
       </c>
       <c r="K20" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L20" s="1">
-        <v>669.6703199999999</v>
-      </c>
-      <c r="M20" t="s">
-        <v>67</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>669.67</v>
+      </c>
+      <c r="L20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F21">
         <v>335</v>
       </c>
       <c r="G21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H21">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I21" s="1">
-        <v>1.649</v>
+        <v>552.415</v>
       </c>
       <c r="J21">
-        <v>552.415</v>
+        <v>1.75</v>
       </c>
       <c r="K21" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L21" s="1">
         <v>586.25</v>
       </c>
-      <c r="M21" t="s">
-        <v>68</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="L21" t="s">
+        <v>67</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F22">
         <v>525.549</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H22">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I22" s="1">
-        <v>1.649</v>
+        <v>866.63</v>
       </c>
       <c r="J22">
-        <v>866.630301</v>
+        <v>1.75</v>
       </c>
       <c r="K22" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L22" s="1">
-        <v>919.71075</v>
-      </c>
-      <c r="M22" t="s">
-        <v>69</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>919.711</v>
+      </c>
+      <c r="L22" t="s">
+        <v>68</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F23">
         <v>54.331</v>
       </c>
       <c r="G23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H23">
-        <v>1.653</v>
+        <v>1.683</v>
       </c>
       <c r="I23" s="1">
-        <v>1.683</v>
+        <v>91.43899999999999</v>
       </c>
       <c r="J23">
-        <v>91.43907299999999</v>
+        <v>1.75</v>
       </c>
       <c r="K23" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L23" s="1">
-        <v>95.07925</v>
-      </c>
-      <c r="M23" t="s">
-        <v>70</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>95.07899999999999</v>
+      </c>
+      <c r="L23" t="s">
+        <v>69</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F24">
         <v>470</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H24">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I24" s="1">
-        <v>1.704</v>
+        <v>800.88</v>
       </c>
       <c r="J24">
-        <v>800.88</v>
+        <v>1.75</v>
       </c>
       <c r="K24" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L24" s="1">
         <v>822.5</v>
       </c>
-      <c r="M24" t="s">
-        <v>71</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="L24" t="s">
+        <v>70</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F25">
         <v>513.183</v>
       </c>
       <c r="G25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H25">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I25" s="1">
-        <v>1.704</v>
+        <v>874.4640000000001</v>
       </c>
       <c r="J25">
-        <v>874.463832</v>
+        <v>1.75</v>
       </c>
       <c r="K25" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L25" s="1">
-        <v>898.07025</v>
-      </c>
-      <c r="M25" t="s">
-        <v>72</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>898.0700000000001</v>
+      </c>
+      <c r="L25" t="s">
+        <v>71</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F26">
         <v>385.011</v>
       </c>
       <c r="G26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H26">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I26" s="1">
-        <v>1.704</v>
+        <v>656.059</v>
       </c>
       <c r="J26">
-        <v>656.058744</v>
+        <v>1.76</v>
       </c>
       <c r="K26" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L26" s="1">
-        <v>677.61936</v>
-      </c>
-      <c r="M26" t="s">
-        <v>73</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>677.619</v>
+      </c>
+      <c r="L26" t="s">
+        <v>72</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F27">
         <v>462.503</v>
       </c>
       <c r="G27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H27">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I27" s="1">
-        <v>1.719</v>
+        <v>795.043</v>
       </c>
       <c r="J27">
-        <v>795.042657</v>
+        <v>1.77</v>
       </c>
       <c r="K27" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L27" s="1">
-        <v>818.63031</v>
-      </c>
-      <c r="M27" t="s">
-        <v>74</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
+        <v>818.63</v>
+      </c>
+      <c r="L27" t="s">
+        <v>73</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="3" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2032,49 +1948,49 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:14">
       <c r="A31" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="E31" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32" s="6">
         <v>9566.380999999999</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="7">
         <v>26</v>
       </c>
       <c r="D32" s="7">
-        <v>1.56691</v>
-      </c>
-      <c r="E32" s="6">
-        <v>14989.65</v>
-      </c>
-      <c r="F32" s="6">
-        <v>15668.46</v>
+        <v>1.567</v>
+      </c>
+      <c r="E32" s="7">
+        <v>14989.654</v>
+      </c>
+      <c r="F32" s="7">
+        <v>15668.457</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B33" s="9">
         <v>9566.380999999999</v>
@@ -2084,10 +2000,10 @@
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="9">
-        <v>14989.65</v>
+        <v>14989.654</v>
       </c>
       <c r="F33" s="9">
-        <v>15668.46</v>
+        <v>15668.457</v>
       </c>
     </row>
   </sheetData>
